--- a/output/pdf_financials_xlsx/GSVR.xlsx
+++ b/output/pdf_financials_xlsx/GSVR.xlsx
@@ -5568,19 +5568,19 @@
         <v>10.977644</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>18.150184</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>24.573358</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>31.016014</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>31.016</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>38.181</v>
       </c>
     </row>
     <row r="93">
@@ -10474,7 +10474,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSVR.xlsx
+++ b/output/pdf_financials_xlsx/GSVR.xlsx
@@ -910,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.07109799999999999</v>
+        <v>0.121111</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.85144</v>
+        <v>1.815345</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.6646570000000001</v>
+        <v>1.474472</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.346454</v>
+        <v>0.587304</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.199526</v>
@@ -965,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.07109799999999999</v>
+        <v>-0.121111</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.85144</v>
+        <v>-1.815345</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.6646570000000001</v>
+        <v>-1.474472</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.346454</v>
+        <v>-0.587304</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-10.900793</v>
@@ -1026,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000473</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1937,10 +1937,10 @@
         <v>-1.875737</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.348411</v>
+        <v>-1.348884</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.348411</v>
+        <v>-1.348429</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-11.8498</v>
@@ -2047,10 +2047,10 @@
         <v>-1.869899</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.342156</v>
+        <v>-1.342629</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.344772</v>
+        <v>-1.34479</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-10.33122</v>
@@ -2287,25 +2287,25 @@
         <v>0.19161</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.027648</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003679</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001041</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.055816</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.119009</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.041022</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.544279</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>8.234043</v>
@@ -2397,25 +2397,25 @@
         <v>0.628588</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.029648</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.00368</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001041</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.055816</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.119009</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.041022</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.544279</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>8.234043</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.032306</v>
+        <v>0.004658</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.003678</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.001041</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.047761</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.153707</v>
+        <v>0.034698</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.046456</v>
+        <v>0.005434</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.547324</v>
+        <v>0.003045</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>1.622935</v>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -53782,7 +53782,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -54068,7 +54068,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSVR.xlsx
+++ b/output/pdf_financials_xlsx/GSVR.xlsx
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.064066</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.067342</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.04015</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0.120595</v>
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.901629</v>
+        <v>0.965695</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.901629</v>
+        <v>0.968971</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.047338</v>
+        <v>0.087488</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.24119</v>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>7.987353</v>
+        <v>7.923287</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.951391</v>
+        <v>3.884049</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.028464</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>1.181134</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>2.35713</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>2.076</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="111">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005136</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06382500000000001</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.046243</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013367</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6556,10 +6556,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031479</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>0.005448</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.352</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
     </row>
     <row r="116">
@@ -7849,16 +7849,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005136</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06382500000000001</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.046243</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013367</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -7873,10 +7873,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031479</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005448</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7904,16 +7904,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.086175</v>
+        <v>-2.091311</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.151665</v>
+        <v>-2.21549</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.089305</v>
+        <v>-3.135548</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.392528</v>
+        <v>-1.405895</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.132069</v>
@@ -7928,10 +7928,10 @@
         <v>-0.045364</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.614768</v>
+        <v>-1.646247</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.982986</v>
+        <v>-0.988434</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.5883620000000001</v>
@@ -26030,7 +26030,11 @@
           <t>Accretion 19</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -28160,7 +28164,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -30112,7 +30120,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -35142,7 +35154,11 @@
           <t>Disposition (purchase) of equipment</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -37166,7 +37182,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -42136,7 +42156,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -43192,7 +43216,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -43944,7 +43972,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E378" s="5" t="n">
         <v>-0.005136</v>
       </c>
@@ -45466,7 +45498,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -67898,7 +67934,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
